--- a/models/NVS.xlsx
+++ b/models/NVS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zjult\ClaudeCode\biopharma-financial-models\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5CD223-F8E1-4887-A1D1-8EF5808403B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E16196C-69A0-4526-9F7D-0A0735EBFF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44055" yWindow="1530" windowWidth="19995" windowHeight="13635" xr2:uid="{F0652295-93CC-4638-BE61-190A5FE627D9}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Novartis AG (NVS) - Daily Stock Price, Last 5 Years</t>
   </si>
   <si>
-    <t>Source: Nasdaq historical quotes (nasdaq.com/market-activity/stocks/nvs), retrieved 2026-10-05. Prices in USD per ADS; not split/dividend adjusted beyond Nasdaq's own presentation.</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -66,6 +63,9 @@
   </si>
   <si>
     <t>Volume (shares)</t>
+  </si>
+  <si>
+    <t>Source: Nasdaq historical quotes (nasdaq.com/market-activity/stocks/nvs), retrieved 2026-10-05. USD per ADS. Prices before 2023-10-03 are as adjusted by Nasdaq (4-decimal values), consistent with the Oct 2023 Sandoz spin-off.</t>
   </si>
 </sst>
 </file>
@@ -503,27 +503,27 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">

--- a/models/NVS.xlsx
+++ b/models/NVS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zjult\ClaudeCode\biopharma-financial-models\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E16196C-69A0-4526-9F7D-0A0735EBFF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC2CCF6-9A71-4CD2-9DC2-26913298F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44055" yWindow="1530" windowWidth="19995" windowHeight="13635" xr2:uid="{F0652295-93CC-4638-BE61-190A5FE627D9}"/>
   </bookViews>
@@ -17,6 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock Price'!$A$4:$F$1258</definedName>
+    <definedName name="ChartClose">INDEX(PxClose,MIN('Stock Price'!$I$9,COUNT(PxDates))):INDEX(PxClose,MAX('Stock Price'!$I$10,1))</definedName>
+    <definedName name="ChartDates">INDEX(PxDates,MIN('Stock Price'!$I$9,COUNT(PxDates))):INDEX(PxDates,MAX('Stock Price'!$I$10,1))</definedName>
+    <definedName name="PxClose">'Stock Price'!$E$5:INDEX('Stock Price'!$E:$E,COUNT('Stock Price'!$A:$A)+4)</definedName>
+    <definedName name="PxDates">'Stock Price'!$A$5:INDEX('Stock Price'!$A:$A,COUNT('Stock Price'!$A:$A)+4)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Novartis AG (NVS) - Daily Stock Price, Last 5 Years</t>
   </si>
@@ -67,16 +71,62 @@
   <si>
     <t>Source: Nasdaq historical quotes (nasdaq.com/market-activity/stocks/nvs), retrieved 2026-10-05. USD per ADS. Prices before 2023-10-03 are as adjusted by Nasdaq (4-decimal values), consistent with the Oct 2023 Sandoz spin-off.</t>
   </si>
+  <si>
+    <t>Price Chart</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Enter a date (yellow cells are inputs)</t>
+  </si>
+  <si>
+    <t>Leave blank to use today</t>
+  </si>
+  <si>
+    <t>Calculations</t>
+  </si>
+  <si>
+    <t>End date used</t>
+  </si>
+  <si>
+    <t>Start row #</t>
+  </si>
+  <si>
+    <t>End row #</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>First trading day</t>
+  </si>
+  <si>
+    <t>Last trading day</t>
+  </si>
+  <si>
+    <t>Start close ($)</t>
+  </si>
+  <si>
+    <t>End close ($)</t>
+  </si>
+  <si>
+    <t>% change</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,8 +160,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,8 +187,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -142,11 +211,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -154,11 +232,47 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -169,6 +283,7735 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>NVS Daily Close ($)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Close ($)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="0060B0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!ChartDates</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd</c:formatCode>
+                <c:ptCount val="1254"/>
+                <c:pt idx="0">
+                  <c:v>44474</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44475</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44476</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44477</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44480</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44481</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44482</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44483</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44484</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44487</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44488</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44489</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44490</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44491</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44494</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>44495</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>44496</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44497</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44498</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44501</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44502</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44503</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44504</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44505</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44508</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44509</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>44510</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44511</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>44512</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44515</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44516</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44517</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>44518</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>44519</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44522</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>44523</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>44524</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>44526</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>44529</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>44530</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>44531</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>44532</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>44533</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44536</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44537</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>44538</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>44539</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>44540</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>44543</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>44544</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>44545</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>44546</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>44547</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>44550</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>44551</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>44552</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>44553</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>44557</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>44558</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>44559</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>44560</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>44561</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>44564</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>44565</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>44566</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>44567</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>44568</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>44571</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>44572</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>44573</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>44574</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>44575</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>44579</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>44580</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>44581</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>44582</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>44585</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>44586</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>44587</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>44588</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>44589</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>44592</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>44593</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>44594</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>44595</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>44596</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>44599</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>44600</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>44601</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>44602</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>44603</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>44606</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>44607</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>44608</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>44609</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>44610</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>44614</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>44615</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>44616</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>44617</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>44620</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>44621</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>44622</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>44623</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>44624</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>44627</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>44628</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>44629</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>44630</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>44631</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>44634</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>44635</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>44636</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>44637</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>44638</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>44641</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>44642</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>44643</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>44644</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>44645</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>44648</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>44649</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>44650</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>44651</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>44652</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>44655</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>44656</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>44657</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>44658</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>44659</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>44662</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>44663</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>44664</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>44665</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>44669</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>44670</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>44671</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>44672</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>44673</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>44676</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>44677</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>44678</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>44679</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>44680</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>44683</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>44684</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>44685</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>44686</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>44687</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>44690</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>44691</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>44692</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>44693</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>44694</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>44697</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>44698</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>44699</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>44700</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>44701</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>44704</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>44705</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>44706</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>44707</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>44708</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>44712</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>44713</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>44714</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>44715</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>44718</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>44719</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>44720</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>44721</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>44722</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>44725</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>44726</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>44727</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>44728</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>44729</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>44733</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>44734</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>44735</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>44736</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>44739</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>44740</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>44741</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>44742</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>44743</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>44747</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>44748</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>44749</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>44750</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>44753</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>44754</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>44755</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>44756</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>44757</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>44760</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>44761</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>44762</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>44763</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>44764</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>44767</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>44768</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>44769</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>44770</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>44771</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>44774</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>44775</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>44776</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>44777</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>44778</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>44781</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>44782</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>44783</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>44784</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>44785</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>44788</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>44789</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>44790</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>44791</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>44792</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>44795</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>44796</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>44797</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>44798</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>44799</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>44802</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>44803</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>44804</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>44805</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>44806</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>44810</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>44811</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>44812</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>44813</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>44816</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>44817</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>44818</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>44819</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>44820</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>44823</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>44824</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>44825</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>44826</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>44827</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>44830</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>44831</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>44832</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>44833</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>44834</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>44837</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>44838</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>44839</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>44840</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>44841</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>44844</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>44845</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>44846</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>44847</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>44848</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>44851</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>44852</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>44853</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>44854</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>44855</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>44858</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>44859</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>44860</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>44861</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>44862</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>44865</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>44866</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>44867</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>44868</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>44869</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>44872</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>44873</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>44874</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>44875</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>44876</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>44879</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>44880</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>44881</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>44882</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>44883</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>44886</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>44887</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>44888</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>44890</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>44893</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>44894</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>44895</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>44896</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>44897</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>44900</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>44901</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>44902</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>44903</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>44904</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>44907</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>44908</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>44909</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>44910</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>44911</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>44914</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>44915</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>44916</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>44917</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>44918</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>44922</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>44923</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>44924</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>44925</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>44929</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>44930</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>44931</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>44932</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>44935</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>44936</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>44937</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>44938</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>44939</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>44943</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>44944</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>44945</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>44946</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>44949</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>44950</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>44951</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>44952</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>44953</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>44956</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>44957</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>44958</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>44959</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>44960</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>44963</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>44964</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>44965</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>44966</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>44967</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>44970</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>44971</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>44972</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>44973</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>44974</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>44978</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>44979</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>44980</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>44981</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>44984</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>44985</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>44986</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>44987</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>44988</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>44991</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>44992</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>44993</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>44994</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>44995</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>44998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>44999</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>45001</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>45002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>45005</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>45006</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>45007</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>45008</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>45009</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>45012</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>45013</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>45014</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>45015</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>45016</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>45019</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>45020</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>45021</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>45022</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>45026</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>45027</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>45028</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>45029</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>45030</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>45033</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>45034</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>45035</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>45036</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>45037</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>45040</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>45041</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>45042</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>45043</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>45044</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>45047</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>45048</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>45049</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>45050</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>45051</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>45054</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>45055</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>45056</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>45057</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>45058</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>45061</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>45062</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>45063</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>45064</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>45065</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>45068</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>45069</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>45070</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>45071</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>45072</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>45076</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>45077</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>45078</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>45079</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>45082</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>45083</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>45084</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>45085</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>45086</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>45089</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>45090</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>45091</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>45092</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>45093</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>45097</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>45098</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>45099</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>45100</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>45103</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>45104</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>45105</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>45106</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>45107</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>45110</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>45112</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>45113</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>45114</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>45117</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>45118</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>45119</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>45120</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>45121</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>45124</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>45125</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>45126</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>45127</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>45128</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>45131</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>45132</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>45133</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>45134</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>45135</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>45138</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>45139</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>45140</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>45141</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>45142</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>45145</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>45146</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>45147</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>45148</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>45149</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>45152</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>45153</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>45154</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>45155</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>45156</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>45159</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>45160</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>45161</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>45162</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>45163</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>45166</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>45167</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>45168</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>45169</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>45170</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>45174</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>45175</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>45176</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>45177</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>45180</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>45181</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>45182</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>45183</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>45184</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>45187</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>45188</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>45189</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>45190</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>45191</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>45194</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>45195</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>45196</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>45197</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>45198</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>45201</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>45202</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>45203</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>45204</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>45205</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>45208</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>45209</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>45210</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>45211</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>45212</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>45215</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>45216</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>45217</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>45218</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>45219</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>45222</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>45223</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>45224</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>45225</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>45226</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>45229</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>45230</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>45231</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>45232</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>45233</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>45236</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>45237</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>45238</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>45239</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>45240</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>45243</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>45244</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>45245</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>45246</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>45247</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>45250</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>45251</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>45252</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>45254</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>45257</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>45258</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>45259</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>45260</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>45261</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>45264</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>45265</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>45266</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>45267</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>45268</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>45271</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>45272</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>45273</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>45274</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>45275</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>45278</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>45279</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>45280</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>45281</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>45282</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>45286</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>45287</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>45288</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>45289</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>45293</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>45294</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>45295</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>45296</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>45299</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>45300</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>45301</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>45302</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>45303</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>45307</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>45308</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>45309</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>45310</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>45313</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>45314</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>45315</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>45316</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>45317</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>45320</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>45321</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>45322</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>45323</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>45324</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>45327</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>45328</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>45329</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>45330</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>45331</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>45334</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>45335</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>45336</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>45337</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>45338</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>45342</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>45343</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>45344</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>45345</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>45348</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>45349</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>45350</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>45351</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>45352</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>45355</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>45356</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>45357</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>45358</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>45359</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>45362</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>45363</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>45364</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>45365</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>45366</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>45369</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>45370</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>45371</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>45372</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>45373</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>45376</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>45377</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>45378</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>45379</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>45383</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>45384</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>45385</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>45386</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>45387</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>45390</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>45391</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>45392</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>45393</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>45394</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>45397</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>45398</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>45399</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>45400</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>45401</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>45404</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>45405</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>45406</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>45407</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>45408</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>45411</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>45412</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>45413</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>45414</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>45415</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>45418</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>45419</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>45420</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>45421</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>45422</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>45425</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>45426</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>45427</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>45428</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>45429</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>45432</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>45433</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>45434</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>45435</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>45436</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>45440</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>45441</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>45442</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>45443</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>45446</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>45447</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>45448</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>45449</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>45450</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>45453</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>45454</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>45455</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>45456</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>45457</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>45460</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>45461</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>45463</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>45464</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>45467</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>45468</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>45469</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>45470</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>45471</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>45474</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>45475</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>45476</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>45478</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>45481</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>45482</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>45483</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>45484</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>45485</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>45488</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>45489</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>45490</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>45491</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>45492</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>45495</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>45496</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>45497</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>45498</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>45499</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>45502</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>45503</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>45504</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>45505</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>45506</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>45509</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>45510</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>45511</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>45512</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>45513</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>45516</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>45517</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>45518</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>45519</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>45520</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>45523</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>45524</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>45525</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>45526</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>45527</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>45530</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>45531</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>45532</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>45533</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>45534</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>45538</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>45539</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>45540</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>45541</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>45544</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>45545</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>45546</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>45547</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>45548</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>45551</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>45552</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>45553</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>45554</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>45555</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>45587</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>45588</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>45589</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>45590</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>45593</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>45594</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>45595</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>45596</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>45600</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>45601</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>45602</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>45603</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>45604</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>45607</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>45608</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>45609</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>45610</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>45611</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>45614</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>45615</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>45616</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>45617</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>45618</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>45621</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>45622</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>45623</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>45625</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>45628</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>45629</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>45630</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>45631</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>45632</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>45635</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>45636</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>45637</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>45638</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>45639</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>45642</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>45643</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>45644</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>45645</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>45646</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>45649</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>45650</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>45652</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>45653</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>45656</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>45657</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>45659</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>45660</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>45663</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>45664</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>45665</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>45667</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>45670</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>45671</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>45672</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>45673</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>45674</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>45678</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>45679</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>45680</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>45681</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>45684</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>45685</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>45686</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>45688</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>45691</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>45692</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>45693</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>45694</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>45695</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>45698</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>45699</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>45700</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>45701</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>45702</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>45706</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>45707</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>45709</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>45712</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>45713</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>45714</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>45715</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>45716</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>45719</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>45720</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>45721</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>45722</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>45723</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>45726</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>45727</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>45728</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>45729</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>45734</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>45735</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>45736</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>45737</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>45740</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>45741</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>45742</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>45743</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>45744</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>45747</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>45749</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>45755</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>45756</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>45758</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>45761</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>45762</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>45763</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>45764</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>45768</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>45769</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>45770</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>45771</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>45772</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>45775</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>45776</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>45777</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>45779</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>45782</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>45783</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>45784</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>45785</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>45786</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>45789</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>45790</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>45791</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>45792</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>45793</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>45796</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>45797</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>45798</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>45799</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>45800</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>45804</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>45805</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>45806</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>45807</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>45810</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>45811</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>45812</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>45813</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>45814</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>45817</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>45818</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>45819</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>45820</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>45821</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>45824</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>45825</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>45826</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>45828</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>45831</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>45832</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>45833</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>45834</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>45835</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>45838</c:v>
+                </c:pt>
+                <c:pt idx="937">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="938">
+                  <c:v>45840</c:v>
+                </c:pt>
+                <c:pt idx="939">
+                  <c:v>45841</c:v>
+                </c:pt>
+                <c:pt idx="940">
+                  <c:v>45845</c:v>
+                </c:pt>
+                <c:pt idx="941">
+                  <c:v>45846</c:v>
+                </c:pt>
+                <c:pt idx="942">
+                  <c:v>45847</c:v>
+                </c:pt>
+                <c:pt idx="943">
+                  <c:v>45848</c:v>
+                </c:pt>
+                <c:pt idx="944">
+                  <c:v>45849</c:v>
+                </c:pt>
+                <c:pt idx="945">
+                  <c:v>45852</c:v>
+                </c:pt>
+                <c:pt idx="946">
+                  <c:v>45853</c:v>
+                </c:pt>
+                <c:pt idx="947">
+                  <c:v>45854</c:v>
+                </c:pt>
+                <c:pt idx="948">
+                  <c:v>45855</c:v>
+                </c:pt>
+                <c:pt idx="949">
+                  <c:v>45856</c:v>
+                </c:pt>
+                <c:pt idx="950">
+                  <c:v>45859</c:v>
+                </c:pt>
+                <c:pt idx="951">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="952">
+                  <c:v>45861</c:v>
+                </c:pt>
+                <c:pt idx="953">
+                  <c:v>45862</c:v>
+                </c:pt>
+                <c:pt idx="954">
+                  <c:v>45863</c:v>
+                </c:pt>
+                <c:pt idx="955">
+                  <c:v>45866</c:v>
+                </c:pt>
+                <c:pt idx="956">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="957">
+                  <c:v>45868</c:v>
+                </c:pt>
+                <c:pt idx="958">
+                  <c:v>45869</c:v>
+                </c:pt>
+                <c:pt idx="959">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="960">
+                  <c:v>45873</c:v>
+                </c:pt>
+                <c:pt idx="961">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="962">
+                  <c:v>45875</c:v>
+                </c:pt>
+                <c:pt idx="963">
+                  <c:v>45876</c:v>
+                </c:pt>
+                <c:pt idx="964">
+                  <c:v>45877</c:v>
+                </c:pt>
+                <c:pt idx="965">
+                  <c:v>45880</c:v>
+                </c:pt>
+                <c:pt idx="966">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="967">
+                  <c:v>45882</c:v>
+                </c:pt>
+                <c:pt idx="968">
+                  <c:v>45883</c:v>
+                </c:pt>
+                <c:pt idx="969">
+                  <c:v>45884</c:v>
+                </c:pt>
+                <c:pt idx="970">
+                  <c:v>45887</c:v>
+                </c:pt>
+                <c:pt idx="971">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="972">
+                  <c:v>45889</c:v>
+                </c:pt>
+                <c:pt idx="973">
+                  <c:v>45890</c:v>
+                </c:pt>
+                <c:pt idx="974">
+                  <c:v>45891</c:v>
+                </c:pt>
+                <c:pt idx="975">
+                  <c:v>45894</c:v>
+                </c:pt>
+                <c:pt idx="976">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="977">
+                  <c:v>45896</c:v>
+                </c:pt>
+                <c:pt idx="978">
+                  <c:v>45897</c:v>
+                </c:pt>
+                <c:pt idx="979">
+                  <c:v>45898</c:v>
+                </c:pt>
+                <c:pt idx="980">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="981">
+                  <c:v>45903</c:v>
+                </c:pt>
+                <c:pt idx="982">
+                  <c:v>45904</c:v>
+                </c:pt>
+                <c:pt idx="983">
+                  <c:v>45905</c:v>
+                </c:pt>
+                <c:pt idx="984">
+                  <c:v>45908</c:v>
+                </c:pt>
+                <c:pt idx="985">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="986">
+                  <c:v>45910</c:v>
+                </c:pt>
+                <c:pt idx="987">
+                  <c:v>45911</c:v>
+                </c:pt>
+                <c:pt idx="988">
+                  <c:v>45912</c:v>
+                </c:pt>
+                <c:pt idx="989">
+                  <c:v>45915</c:v>
+                </c:pt>
+                <c:pt idx="990">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="991">
+                  <c:v>45917</c:v>
+                </c:pt>
+                <c:pt idx="992">
+                  <c:v>45918</c:v>
+                </c:pt>
+                <c:pt idx="993">
+                  <c:v>45919</c:v>
+                </c:pt>
+                <c:pt idx="994">
+                  <c:v>45922</c:v>
+                </c:pt>
+                <c:pt idx="995">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="996">
+                  <c:v>45924</c:v>
+                </c:pt>
+                <c:pt idx="997">
+                  <c:v>45925</c:v>
+                </c:pt>
+                <c:pt idx="998">
+                  <c:v>45926</c:v>
+                </c:pt>
+                <c:pt idx="999">
+                  <c:v>45929</c:v>
+                </c:pt>
+                <c:pt idx="1000">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="1001">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="1002">
+                  <c:v>45932</c:v>
+                </c:pt>
+                <c:pt idx="1003">
+                  <c:v>45933</c:v>
+                </c:pt>
+                <c:pt idx="1004">
+                  <c:v>45936</c:v>
+                </c:pt>
+                <c:pt idx="1005">
+                  <c:v>45937</c:v>
+                </c:pt>
+                <c:pt idx="1006">
+                  <c:v>45938</c:v>
+                </c:pt>
+                <c:pt idx="1007">
+                  <c:v>45939</c:v>
+                </c:pt>
+                <c:pt idx="1008">
+                  <c:v>45940</c:v>
+                </c:pt>
+                <c:pt idx="1009">
+                  <c:v>45943</c:v>
+                </c:pt>
+                <c:pt idx="1010">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="1011">
+                  <c:v>45945</c:v>
+                </c:pt>
+                <c:pt idx="1012">
+                  <c:v>45946</c:v>
+                </c:pt>
+                <c:pt idx="1013">
+                  <c:v>45947</c:v>
+                </c:pt>
+                <c:pt idx="1014">
+                  <c:v>45950</c:v>
+                </c:pt>
+                <c:pt idx="1015">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="1016">
+                  <c:v>45952</c:v>
+                </c:pt>
+                <c:pt idx="1017">
+                  <c:v>45953</c:v>
+                </c:pt>
+                <c:pt idx="1018">
+                  <c:v>45954</c:v>
+                </c:pt>
+                <c:pt idx="1019">
+                  <c:v>45957</c:v>
+                </c:pt>
+                <c:pt idx="1020">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="1021">
+                  <c:v>45959</c:v>
+                </c:pt>
+                <c:pt idx="1022">
+                  <c:v>45960</c:v>
+                </c:pt>
+                <c:pt idx="1023">
+                  <c:v>45961</c:v>
+                </c:pt>
+                <c:pt idx="1024">
+                  <c:v>45964</c:v>
+                </c:pt>
+                <c:pt idx="1025">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="1026">
+                  <c:v>45966</c:v>
+                </c:pt>
+                <c:pt idx="1027">
+                  <c:v>45967</c:v>
+                </c:pt>
+                <c:pt idx="1028">
+                  <c:v>45968</c:v>
+                </c:pt>
+                <c:pt idx="1029">
+                  <c:v>45971</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="1031">
+                  <c:v>45973</c:v>
+                </c:pt>
+                <c:pt idx="1032">
+                  <c:v>45974</c:v>
+                </c:pt>
+                <c:pt idx="1033">
+                  <c:v>45975</c:v>
+                </c:pt>
+                <c:pt idx="1034">
+                  <c:v>45978</c:v>
+                </c:pt>
+                <c:pt idx="1035">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>45980</c:v>
+                </c:pt>
+                <c:pt idx="1037">
+                  <c:v>45981</c:v>
+                </c:pt>
+                <c:pt idx="1038">
+                  <c:v>45982</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>45985</c:v>
+                </c:pt>
+                <c:pt idx="1040">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="1041">
+                  <c:v>45987</c:v>
+                </c:pt>
+                <c:pt idx="1042">
+                  <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="1043">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="1044">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="1045">
+                  <c:v>45994</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>45995</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>45996</c:v>
+                </c:pt>
+                <c:pt idx="1048">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="1049">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="1050">
+                  <c:v>46001</c:v>
+                </c:pt>
+                <c:pt idx="1051">
+                  <c:v>46002</c:v>
+                </c:pt>
+                <c:pt idx="1052">
+                  <c:v>46003</c:v>
+                </c:pt>
+                <c:pt idx="1053">
+                  <c:v>46006</c:v>
+                </c:pt>
+                <c:pt idx="1054">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="1055">
+                  <c:v>46008</c:v>
+                </c:pt>
+                <c:pt idx="1056">
+                  <c:v>46009</c:v>
+                </c:pt>
+                <c:pt idx="1057">
+                  <c:v>46010</c:v>
+                </c:pt>
+                <c:pt idx="1058">
+                  <c:v>46013</c:v>
+                </c:pt>
+                <c:pt idx="1059">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="1060">
+                  <c:v>46015</c:v>
+                </c:pt>
+                <c:pt idx="1061">
+                  <c:v>46017</c:v>
+                </c:pt>
+                <c:pt idx="1062">
+                  <c:v>46020</c:v>
+                </c:pt>
+                <c:pt idx="1063">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="1064">
+                  <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="1065">
+                  <c:v>46024</c:v>
+                </c:pt>
+                <c:pt idx="1066">
+                  <c:v>46027</c:v>
+                </c:pt>
+                <c:pt idx="1067">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="1068">
+                  <c:v>46029</c:v>
+                </c:pt>
+                <c:pt idx="1069">
+                  <c:v>46030</c:v>
+                </c:pt>
+                <c:pt idx="1070">
+                  <c:v>46031</c:v>
+                </c:pt>
+                <c:pt idx="1071">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="1072">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="1073">
+                  <c:v>46036</c:v>
+                </c:pt>
+                <c:pt idx="1074">
+                  <c:v>46037</c:v>
+                </c:pt>
+                <c:pt idx="1075">
+                  <c:v>46038</c:v>
+                </c:pt>
+                <c:pt idx="1076">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="1077">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1078">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1079">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="1080">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1081">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="1082">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="1083">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="1084">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="1085">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="1086">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="1087">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="1088">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="1089">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="1090">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="1091">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="1092">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="1093">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="1094">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="1095">
+                  <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="1096">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="1097">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="1098">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="1099">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="1100">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="1101">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="1102">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="1103">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="1104">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="1105">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="1106">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="1107">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="1108">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="1109">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="1110">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="1111">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="1112">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="1113">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="1114">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="1115">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="1116">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="1117">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="1118">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="1119">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="1120">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="1121">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="1122">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="1123">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="1124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="1125">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="1126">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="1127">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="1128">
+                  <c:v>46118</c:v>
+                </c:pt>
+                <c:pt idx="1129">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="1130">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="1131">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="1132">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="1133">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="1134">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="1135">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="1136">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="1137">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="1138">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="1139">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="1140">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="1141">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="1142">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="1143">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="1144">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="1145">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="1146">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="1147">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="1148">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="1149">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="1150">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="1151">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="1152">
+                  <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="1153">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="1154">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="1155">
+                  <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="1156">
+                  <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="1157">
+                  <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="1158">
+                  <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="1159">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="1160">
+                  <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="1161">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="1162">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="1163">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="1164">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="1165">
+                  <c:v>46170</c:v>
+                </c:pt>
+                <c:pt idx="1166">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="1167">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="1168">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="1169">
+                  <c:v>46176</c:v>
+                </c:pt>
+                <c:pt idx="1170">
+                  <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="1171">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="1172">
+                  <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="1173">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="1174">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="1175">
+                  <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="1176">
+                  <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="1177">
+                  <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="1178">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="1179">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="1180">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="1181">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="1182">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="1183">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="1184">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="1185">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="1186">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="1187">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="1188">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="1189">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="1190">
+                  <c:v>46209</c:v>
+                </c:pt>
+                <c:pt idx="1191">
+                  <c:v>46210</c:v>
+                </c:pt>
+                <c:pt idx="1192">
+                  <c:v>46211</c:v>
+                </c:pt>
+                <c:pt idx="1193">
+                  <c:v>46212</c:v>
+                </c:pt>
+                <c:pt idx="1194">
+                  <c:v>46213</c:v>
+                </c:pt>
+                <c:pt idx="1195">
+                  <c:v>46216</c:v>
+                </c:pt>
+                <c:pt idx="1196">
+                  <c:v>46217</c:v>
+                </c:pt>
+                <c:pt idx="1197">
+                  <c:v>46218</c:v>
+                </c:pt>
+                <c:pt idx="1198">
+                  <c:v>46219</c:v>
+                </c:pt>
+                <c:pt idx="1199">
+                  <c:v>46220</c:v>
+                </c:pt>
+                <c:pt idx="1200">
+                  <c:v>46223</c:v>
+                </c:pt>
+                <c:pt idx="1201">
+                  <c:v>46224</c:v>
+                </c:pt>
+                <c:pt idx="1202">
+                  <c:v>46225</c:v>
+                </c:pt>
+                <c:pt idx="1203">
+                  <c:v>46226</c:v>
+                </c:pt>
+                <c:pt idx="1204">
+                  <c:v>46227</c:v>
+                </c:pt>
+                <c:pt idx="1205">
+                  <c:v>46230</c:v>
+                </c:pt>
+                <c:pt idx="1206">
+                  <c:v>46231</c:v>
+                </c:pt>
+                <c:pt idx="1207">
+                  <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="1208">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="1209">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="1210">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="1211">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="1212">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="1213">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="1214">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="1215">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="1216">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="1217">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="1218">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="1219">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="1220">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="1221">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="1222">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="1223">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="1224">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="1225">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="1226">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="1227">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="1228">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="1229">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="1230">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="1231">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="1232">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="1233">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="1234">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="1235">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="1236">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="1237">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="1238">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="1239">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="1240">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="1241">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="1242">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="1243">
+                  <c:v>46283</c:v>
+                </c:pt>
+                <c:pt idx="1244">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="1245">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="1246">
+                  <c:v>46288</c:v>
+                </c:pt>
+                <c:pt idx="1247">
+                  <c:v>46289</c:v>
+                </c:pt>
+                <c:pt idx="1248">
+                  <c:v>46290</c:v>
+                </c:pt>
+                <c:pt idx="1249">
+                  <c:v>46293</c:v>
+                </c:pt>
+                <c:pt idx="1250">
+                  <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="1251">
+                  <c:v>46295</c:v>
+                </c:pt>
+                <c:pt idx="1252">
+                  <c:v>46296</c:v>
+                </c:pt>
+                <c:pt idx="1253">
+                  <c:v>46297</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!ChartClose</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
+                <c:ptCount val="1254"/>
+                <c:pt idx="0">
+                  <c:v>79.164299999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79.125600000000006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79.793099999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80.131699999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79.657700000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>79.309399999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>79.744799999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.909199999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80.615499999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>79.657700000000006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>80.441299999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>81.718299999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>81.911799999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>82.153700000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>80.644499999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>82.076300000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>80.034999999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>80.596100000000007</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>80.063999999999993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>81.311999999999998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>81.021799999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>80.867000000000004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>80.963700000000003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>80.924999999999997</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>80.509</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>80.383300000000006</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>80.460700000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>80.141400000000004</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>79.802800000000005</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>79.599699999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>79.241699999999994</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>79.231999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>79.299800000000005</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>78.999899999999997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>78.670900000000003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>79.977000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>79.241699999999994</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>78.071100000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>77.655100000000004</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>77.103700000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>77.219800000000006</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>77.345600000000005</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>77.393900000000002</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>77.906700000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>78.0518</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>78.709599999999995</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>77.819599999999994</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>78.042100000000005</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78.216200000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>77.964699999999993</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>78.864400000000003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>83.266199999999998</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>83.101699999999994</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>82.569599999999994</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>83.188800000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>83.498400000000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>83.837000000000003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>84.756</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>85.259100000000004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>85.249399999999994</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>84.610900000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>84.620599999999996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>85.007599999999996</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>84.620599999999996</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>85.162300000000002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>85.413899999999998</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>86.400599999999997</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>87.145600000000002</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>86.942400000000006</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>86.864999999999995</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>87.668000000000006</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>87.600300000000004</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>86.623199999999997</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>85.955600000000004</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>85.317099999999996</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>84.194900000000004</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>82.356800000000007</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>81.786000000000001</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>81.495800000000003</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>82.366500000000002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>83.111400000000003</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>84.078800000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>85.307500000000005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>83.111400000000003</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>83.604799999999997</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>83.469399999999993</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>84.369100000000003</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>84.311000000000007</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>84.359399999999994</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>83.034000000000006</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>82.782499999999999</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>82.898600000000002</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>83.604799999999997</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>85.075299999999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>83.837000000000003</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>83.575800000000001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>83.034000000000006</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>83.701499999999996</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>82.888900000000007</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>84.775400000000005</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>84.610900000000001</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>84.281999999999996</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>84.823700000000002</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>83.3339</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>81.979500000000002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>80.818600000000004</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>77.500299999999996</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>79.4739</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>80.267200000000003</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>79.686700000000002</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>81.331299999999999</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>81.969800000000006</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>81.882800000000003</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>83.624099999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>83.962699999999998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>83.275899999999993</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>83.111400000000003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>82.763099999999994</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>83.817599999999999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>84.030500000000004</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>84.156199999999998</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>84.659300000000002</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>85.0946</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>84.891499999999994</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>84.833399999999997</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>84.485100000000003</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>85.297799999999995</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>87.697000000000003</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>88.422600000000003</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>89.709199999999996</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>90.695999999999998</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>89.651200000000003</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>89.912400000000005</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>89.506100000000004</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>89.254499999999993</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>88.616</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>88.267799999999994</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>87.019800000000004</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>86.303899999999999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>87.493799999999993</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>86.061999999999998</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>86.497399999999999</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>87.281000000000006</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>85.162300000000002</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>84.794700000000006</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>84.630300000000005</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>85.394499999999994</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>83.401600000000002</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>83.024299999999997</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>80.760599999999997</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>81.640900000000002</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>81.302300000000002</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>82.598699999999994</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>83.024299999999997</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>84.9495</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>85.055899999999994</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>84.823700000000002</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>85.762100000000004</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>86.507099999999994</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>87.754999999999995</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>88.935299999999998</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>88.2774</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>88.287099999999995</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>88.480599999999995</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>87.977500000000006</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>86.719899999999996</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>86.864999999999995</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>86.216800000000006</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>85.781499999999994</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>85.984700000000004</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>84.504499999999993</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>83.566100000000006</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>82.289100000000005</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>79.841499999999996</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>77.897000000000006</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>78.709599999999995</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>79.183700000000002</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>78.419399999999996</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>78.835400000000007</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>78.854699999999994</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>79.193299999999994</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>82.066599999999994</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>82.501900000000006</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>81.428100000000001</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>82.008499999999998</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>81.776399999999995</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>81.611900000000006</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>81.534499999999994</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>81.002399999999994</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>81.650599999999997</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>81.592500000000001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>81.737700000000004</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>81.205600000000004</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>80.305899999999994</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>79.909199999999998</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>81.882800000000003</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>80.006</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>83.198499999999996</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>81.476500000000001</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>83.092100000000002</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>83.072699999999998</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>83.275899999999993</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>84.011099999999999</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>83.924000000000007</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>84.417400000000001</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>83.034000000000006</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>82.840500000000006</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>82.289100000000005</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>82.095600000000005</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>82.453599999999994</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>82.782499999999999</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>83.1404</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>84.311000000000007</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>84.581900000000005</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>82.792199999999994</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>82.888900000000007</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>82.598699999999994</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>83.024299999999997</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>82.443899999999999</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>82.153700000000001</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>82.966300000000004</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>81.640900000000002</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>80.760599999999997</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>80.886300000000006</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>80.692800000000005</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>79.986599999999996</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>79.570599999999999</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>78.129199999999997</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>77.897000000000006</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>77.713200000000001</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>77.103700000000003</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>77.171400000000006</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>78.303299999999993</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>78.612899999999996</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>79.909199999999998</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>80.8767</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>79.2804</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>78.274299999999997</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>78.109800000000007</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>78.022800000000004</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>78.100099999999998</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>76.9876</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>75.014099999999999</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>74.627099999999999</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>73.533900000000003</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>72.179500000000004</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>72.218199999999996</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>73.833799999999997</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>74.075699999999998</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>73.533900000000003</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>74.172399999999996</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>75.681600000000003</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>74.849599999999995</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>73.562899999999999</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>73.185599999999994</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>73.088899999999995</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>73.388800000000003</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>72.856700000000004</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>73.533900000000003</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>73.108199999999997</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>74.752899999999997</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>74.965699999999998</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>74.017600000000002</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>73.088899999999995</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>74.588399999999993</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>75.1785</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>75.952500000000001</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>77.016599999999997</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>76.948899999999995</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>78.129199999999997</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>78.487099999999998</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>78.419399999999996</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>77.964699999999993</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>77.761499999999998</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>79.057900000000004</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>79.144999999999996</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>79.164299999999997</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>80.267200000000003</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>82.356800000000007</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>81.283000000000001</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>80.731499999999997</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>81.099199999999996</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>80.828299999999999</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>80.741200000000006</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>82.908199999999994</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>83.962699999999998</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>84.843100000000007</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>84.446399999999997</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>84.852800000000002</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>84.823700000000002</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>84.514200000000002</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>86.642499999999998</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>86.894000000000005</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>87.058499999999995</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>87.996899999999997</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>87.784099999999995</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>88.741799999999998</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>88.596699999999998</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>87.987200000000001</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>87.919499999999999</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>88.238799999999998</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>89.515799999999999</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>87.929199999999994</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>87.532499999999999</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>87.251999999999995</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>87.426100000000005</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>87.938900000000004</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>87.938900000000004</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>87.909800000000004</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>88.1614</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>87.880799999999994</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>88.616</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>87.764700000000005</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>89.206199999999995</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>88.848200000000006</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>87.842100000000002</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>89.283600000000007</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>87.019800000000004</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>87.493799999999993</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>87.522900000000007</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>87.609899999999996</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>88.093599999999995</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>89.370599999999996</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>89.157799999999995</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>89.225499999999997</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>89.070700000000002</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>89.206199999999995</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>89.022400000000005</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>89.786600000000007</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>86.913399999999996</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>86.574799999999996</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>86.719899999999996</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>87.668000000000006</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>85.355800000000002</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>83.295199999999994</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>83.053399999999996</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>82.685699999999997</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>83.5274</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>84.0595</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>83.498400000000004</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>83.662800000000004</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>84.639899999999997</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>84.697999999999993</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>84.34</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>83.159800000000004</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>84.214299999999994</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>83.933700000000002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>83.856300000000005</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>83.7209</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>82.8309</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>82.763099999999994</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>81.3797</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>81.089500000000001</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>82.347099999999998</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>81.921499999999995</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>82.153700000000001</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>81.244299999999996</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>80.576800000000006</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>77.423000000000002</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>78.042100000000005</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>78.951499999999996</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>79.415800000000004</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>79.4255</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>80.083399999999997</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>79.512600000000006</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>80.712199999999996</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>80.944400000000002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>79.290099999999995</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>79.822199999999995</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>80.867000000000004</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>87.338999999999999</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>87.987200000000001</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>87.251999999999995</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>88.596699999999998</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>89.003</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>89.506100000000004</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>90.434799999999996</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>91.972999999999999</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>93.124200000000002</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>92.582499999999996</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>92.679199999999994</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>93.327399999999997</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>95.020399999999995</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>94.691500000000005</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>94.778499999999994</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>94.149699999999996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>94.826899999999995</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>95.388000000000005</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>97.032600000000002</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>97.313199999999995</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>100.6508</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>99.199700000000007</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>99.306100000000001</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>99.228700000000003</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>99.199700000000007</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>100.1671</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>101.0474</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>101.2119</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>101.3087</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>101.49250000000001</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>101.2893</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>100.2542</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>100.051</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>99.780100000000004</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>99.760800000000003</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>99.460899999999995</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>97.922700000000006</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>97.081000000000003</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>97.525999999999996</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>97.458299999999994</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>96.984300000000005</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>96.7714</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>94.594700000000003</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>94.6721</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>93.404799999999994</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>93.114599999999996</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>93.946600000000004</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>95.687899999999999</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>96.132900000000006</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>96.413499999999999</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>95.291300000000007</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>97.371200000000002</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>97.642099999999999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>96.742400000000004</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>96.084599999999995</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>96.4328</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>98.087100000000007</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>98.512799999999999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>97.535700000000006</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>97.622799999999998</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>97.264799999999994</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>97.409899999999993</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>96.2684</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>95.949100000000001</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>95.233199999999997</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>96.1233</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>97.622799999999998</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>95.552499999999995</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>95.726600000000005</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>94.8172</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>91.644099999999995</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>93.404799999999994</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>93.994900000000001</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>94.5077</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>95.126800000000003</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>95.610500000000002</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>95.716899999999995</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>100.08969999999999</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>99.857500000000002</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>101.70529999999999</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>101.58920000000001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>100.6992</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>101.4054</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>100.5057</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>100.44759999999999</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>100.78619999999999</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>101.4828</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>99.954300000000003</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>99.402799999999999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>98.715999999999994</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>98.483800000000002</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>99.4512</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>99.693100000000001</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>99.9833</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>99.925200000000004</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>100.21550000000001</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>100.0026</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>99.248000000000005</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>98.783699999999996</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>98.4161</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>97.729200000000006</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>99.625299999999996</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>99.248000000000005</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>99.480199999999996</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>97.555000000000007</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>98.464399999999998</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>99.006200000000007</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>99.915599999999998</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>98.590199999999996</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>97.206800000000001</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>97.438999999999993</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>94.894599999999997</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>94.701099999999997</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>95.629900000000006</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>95.136499999999998</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>96.007199999999997</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>97.380899999999997</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>97.497</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>98.512799999999999</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>99.286699999999996</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>98.745000000000005</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>99.557599999999994</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>100.2058</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>98.764300000000006</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>97.845299999999995</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>98.493399999999994</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>98.116200000000006</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>96.993899999999996</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>98.996499999999997</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>98.541799999999995</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>98.232200000000006</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>96.22</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>96.16</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>96.15</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>97.14</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>97.59</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>98.47</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>99.41</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>97.87</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>97.24</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>96.84</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>96.49</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>96.1</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>94.64</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>94.68</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>94.69</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>94.91</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>95.43</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>94.3</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>92.27</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>93.76</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>93.58</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>94.26</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>94.08</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>92.76</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>93.45</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>93.82</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>94.38</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>93.23</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>93.54</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>94.09</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>94.91</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>93.8</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>94.06</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>94.91</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>95.25</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>96.38</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>97.09</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>98.14</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>97.74</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>97.01</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>97.9</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>98.13</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>98.99</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>96.97</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>97.05</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>95.93</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>96.3</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>97.28</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>98.17</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>99.71</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>98.87</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>97.4</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>98.22</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>98.29</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>97.14</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>98.1</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>98.75</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>98.55</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>99.71</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>99.97</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>100.97</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>104.82</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>105.57</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>106.31</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>107.08</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>106.39</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>107.44</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>107.6</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>107.45</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>107.69</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>108.26</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>108.03</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>108.23</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>108.47</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>107.73</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>107.55</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>106.99</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>107.16</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>107.95</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>107.75</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>103.47</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>105.33</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>103.72</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>103.47</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>103.74</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>103.46</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>101.36</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>101.03</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>100.53</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>99.06</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>99.05</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>99.63</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>100.19</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>102.72</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>102.56</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>102.8</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>103.9</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>103.25</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>103.15</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>102.22</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>100.97</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>102.06</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>101.97</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>102.1</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>102.64</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>99.93</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>100.71</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>101.37</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>99.77</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>98.13</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>97.27</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>95.92</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>96.32</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>96.05</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>96.08</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>96.23</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>95.73</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>95.27</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>95.88</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>96.73</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>95.87</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>94.41</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>94.37</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>96.89</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>95.79</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>95.48</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>95.81</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>94.38</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>94.34</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>93.52</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>94.41</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>93.2</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>93.08</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>92.57</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>94.36</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>95.12</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>97.28</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>98.35</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>99.06</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>97.44</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>97.09</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>97.13</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>97.5</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>97.34</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>97.27</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>97.73</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>99.07</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>99.6</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>100.21</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>102.1</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>102.26</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>103.31</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>103.22</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>102.69</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>102.57</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>102.84</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>102.84</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>101.96</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>101.11</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>100.53</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>99.68</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>99.36</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>100.7</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>103.13</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>102.76</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>104.92</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>105.36</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>106.13</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>105.33</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>105.4</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>104.51</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>105.55</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>106.02</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>105.72</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>104.93</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>104.94</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>105.74</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>105.22</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>106.95</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>107.37</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>107.07</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>106.55</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>106.46</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>106.54</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>106.44</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>106.78</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>108.13</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>108.06</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>108.23</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>109.94</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>110.5</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>111.7</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>110.33</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>110.53</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>111.8</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>107.22</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>106.13</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>108.73</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>107.7</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>109.29</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>109.93</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>110.32</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>110.67</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>111.93</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>111.48</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>112.1</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>112.87</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>109.85</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>110.06</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>111.16</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>111.02</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>111.89</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>111.42</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>112.53</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>113.53</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>113.31</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>114.7</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>115.93</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>117.13</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>117.61</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>117.76</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>118.56</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>119.15</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>119.84</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>119.98</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>120.42</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>120.89</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>118.5</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>119.38</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>116.49</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>116.65</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>117.16</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>116.99</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>115.28</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>115.72</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>115.66</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>116.95</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>115.7</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>115.97</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>115.98</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>115.94</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>116.37</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>116.42</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>116.43</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>115.61</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>115.61</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>115.02</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>114.55</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>114.47</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>113.77</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>113.95</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>113.86</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>113.77</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>115.64</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>114.81</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>116.22</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>116.3</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>116.22</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>116.57</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>116.51</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>117.18</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>115.73</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>114.32</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>114.07</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>113.13</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>113.79</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>115.63</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>110.53</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>109.91</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>108.4</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>109.35</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>110.52</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>109.38</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>106.81</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>107.08</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>106.45</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>105.67</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>104.92</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>103.86</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>103.4</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>103.06</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>103.04</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>103.27</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>103.09</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>103.85</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>104.28</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>103.54</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>103.81</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>104.87</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>105.77</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>104.8</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>104.56</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>101.84</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>102.52</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>101.99</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>101.68</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>100.13</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>99.17</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>98.59</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>98.36</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>97.77</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>99.1</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>96.83</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>96.77</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>97.11</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>98.45</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>98.35</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>98.4</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>98.39</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>97.33</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>97.31</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>97.14</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>97.64</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>97.7</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>98.98</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>100.22</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>99.08</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>99.27</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>99.37</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>99.07</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>97.86</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>97.53</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>99.73</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>98.17</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>100.03</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>99.97</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>103.41</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>101.84</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>102.93</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>104.75</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>104.72</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>105.48</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>105.47</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>109.81</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>106.98</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>106.26</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>106.85</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>107.75</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>107.71</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>105.43</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>106.61</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>106.91</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>107.31</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>109.35</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>109.22</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>109.62</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>108.02</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>108.92</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>109.05</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>110.62</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>111.42</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>111.88</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>112.87</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>115.57</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>115.47</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>111.35</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>108.64</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>109.11</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>109.06</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>112.22</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>112.22</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>111.56</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>113.21</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>112.13</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>111.09</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>110.38</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>110.14</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>111.4</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>112.57</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>111.48</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>109.61</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>110.77</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>112.26</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>105.85</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>102.87</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>101.96</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>103.85</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>103.4</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>107.52</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>109.46</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>109.93</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>109.58</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>110.86</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>110.54</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>111.41</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>110.13</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>111.17</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>112.14</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>112.63</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>113.45</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>113.49</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>111.33</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>114.29</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>113.08</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>110.55</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>111.7</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>110.13</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>108.7</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>108.95</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>106.83</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>104.99</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>108.46</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>109.59</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>110.71</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>112.28</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>112.78</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>112.5</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>112.75</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>113.21</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>111.87</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>112.58</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>115.76</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>116.7</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>115.94</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>116.94</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>117.79</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>118.02</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>118.02</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>118.58</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>118.07</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>120.77</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>119.45</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>118.09</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>116.41</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>115.96</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>115.77</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>117.52</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>118.83</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>120.32</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>120.01</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>121.01</c:v>
+                </c:pt>
+                <c:pt idx="937">
+                  <c:v>123.1</c:v>
+                </c:pt>
+                <c:pt idx="938">
+                  <c:v>123.81</c:v>
+                </c:pt>
+                <c:pt idx="939">
+                  <c:v>121.9</c:v>
+                </c:pt>
+                <c:pt idx="940">
+                  <c:v>122.12</c:v>
+                </c:pt>
+                <c:pt idx="941">
+                  <c:v>121.68</c:v>
+                </c:pt>
+                <c:pt idx="942">
+                  <c:v>122.94</c:v>
+                </c:pt>
+                <c:pt idx="943">
+                  <c:v>123.73</c:v>
+                </c:pt>
+                <c:pt idx="944">
+                  <c:v>121.02</c:v>
+                </c:pt>
+                <c:pt idx="945">
+                  <c:v>121.04</c:v>
+                </c:pt>
+                <c:pt idx="946">
+                  <c:v>119.67</c:v>
+                </c:pt>
+                <c:pt idx="947">
+                  <c:v>118.37</c:v>
+                </c:pt>
+                <c:pt idx="948">
+                  <c:v>114.52</c:v>
+                </c:pt>
+                <c:pt idx="949">
+                  <c:v>114.25</c:v>
+                </c:pt>
+                <c:pt idx="950">
+                  <c:v>114.14</c:v>
+                </c:pt>
+                <c:pt idx="951">
+                  <c:v>116.83</c:v>
+                </c:pt>
+                <c:pt idx="952">
+                  <c:v>117.97</c:v>
+                </c:pt>
+                <c:pt idx="953">
+                  <c:v>117.46</c:v>
+                </c:pt>
+                <c:pt idx="954">
+                  <c:v>117.7</c:v>
+                </c:pt>
+                <c:pt idx="955">
+                  <c:v>116.18</c:v>
+                </c:pt>
+                <c:pt idx="956">
+                  <c:v>117.22</c:v>
+                </c:pt>
+                <c:pt idx="957">
+                  <c:v>116.63</c:v>
+                </c:pt>
+                <c:pt idx="958">
+                  <c:v>113.74</c:v>
+                </c:pt>
+                <c:pt idx="959">
+                  <c:v>115.3</c:v>
+                </c:pt>
+                <c:pt idx="960">
+                  <c:v>117.83</c:v>
+                </c:pt>
+                <c:pt idx="961">
+                  <c:v>117.73</c:v>
+                </c:pt>
+                <c:pt idx="962">
+                  <c:v>113.5</c:v>
+                </c:pt>
+                <c:pt idx="963">
+                  <c:v>115.92</c:v>
+                </c:pt>
+                <c:pt idx="964">
+                  <c:v>116.84</c:v>
+                </c:pt>
+                <c:pt idx="965">
+                  <c:v>118.55</c:v>
+                </c:pt>
+                <c:pt idx="966">
+                  <c:v>119.31</c:v>
+                </c:pt>
+                <c:pt idx="967">
+                  <c:v>121.2</c:v>
+                </c:pt>
+                <c:pt idx="968">
+                  <c:v>122.09</c:v>
+                </c:pt>
+                <c:pt idx="969">
+                  <c:v>124.21</c:v>
+                </c:pt>
+                <c:pt idx="970">
+                  <c:v>124.01</c:v>
+                </c:pt>
+                <c:pt idx="971">
+                  <c:v>124.95</c:v>
+                </c:pt>
+                <c:pt idx="972">
+                  <c:v>127.25</c:v>
+                </c:pt>
+                <c:pt idx="973">
+                  <c:v>126.82</c:v>
+                </c:pt>
+                <c:pt idx="974">
+                  <c:v>126.98</c:v>
+                </c:pt>
+                <c:pt idx="975">
+                  <c:v>125.04</c:v>
+                </c:pt>
+                <c:pt idx="976">
+                  <c:v>126.64</c:v>
+                </c:pt>
+                <c:pt idx="977">
+                  <c:v>126.89</c:v>
+                </c:pt>
+                <c:pt idx="978">
+                  <c:v>126.47</c:v>
+                </c:pt>
+                <c:pt idx="979">
+                  <c:v>126.55</c:v>
+                </c:pt>
+                <c:pt idx="980">
+                  <c:v>126.64</c:v>
+                </c:pt>
+                <c:pt idx="981">
+                  <c:v>128.22999999999999</c:v>
+                </c:pt>
+                <c:pt idx="982">
+                  <c:v>128.41999999999999</c:v>
+                </c:pt>
+                <c:pt idx="983">
+                  <c:v>129.72999999999999</c:v>
+                </c:pt>
+                <c:pt idx="984">
+                  <c:v>128.71</c:v>
+                </c:pt>
+                <c:pt idx="985">
+                  <c:v>128.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="986">
+                  <c:v>126.55</c:v>
+                </c:pt>
+                <c:pt idx="987">
+                  <c:v>127.7</c:v>
+                </c:pt>
+                <c:pt idx="988">
+                  <c:v>124.12</c:v>
+                </c:pt>
+                <c:pt idx="989">
+                  <c:v>123.31</c:v>
+                </c:pt>
+                <c:pt idx="990">
+                  <c:v>122.78</c:v>
+                </c:pt>
+                <c:pt idx="991">
+                  <c:v>122.47</c:v>
+                </c:pt>
+                <c:pt idx="992">
+                  <c:v>122.29</c:v>
+                </c:pt>
+                <c:pt idx="993">
+                  <c:v>122.93</c:v>
+                </c:pt>
+                <c:pt idx="994">
+                  <c:v>123.36</c:v>
+                </c:pt>
+                <c:pt idx="995">
+                  <c:v>122.82</c:v>
+                </c:pt>
+                <c:pt idx="996">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="997">
+                  <c:v>122.23</c:v>
+                </c:pt>
+                <c:pt idx="998">
+                  <c:v>123.65</c:v>
+                </c:pt>
+                <c:pt idx="999">
+                  <c:v>124.1</c:v>
+                </c:pt>
+                <c:pt idx="1000">
+                  <c:v>128.24</c:v>
+                </c:pt>
+                <c:pt idx="1001">
+                  <c:v>131.72</c:v>
+                </c:pt>
+                <c:pt idx="1002">
+                  <c:v>130.97</c:v>
+                </c:pt>
+                <c:pt idx="1003">
+                  <c:v>132.38999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1004">
+                  <c:v>132.25</c:v>
+                </c:pt>
+                <c:pt idx="1005">
+                  <c:v>131.55000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1006">
+                  <c:v>132.31</c:v>
+                </c:pt>
+                <c:pt idx="1007">
+                  <c:v>131.06</c:v>
+                </c:pt>
+                <c:pt idx="1008">
+                  <c:v>130.03</c:v>
+                </c:pt>
+                <c:pt idx="1009">
+                  <c:v>129.12</c:v>
+                </c:pt>
+                <c:pt idx="1010">
+                  <c:v>130.26</c:v>
+                </c:pt>
+                <c:pt idx="1011">
+                  <c:v>129.97</c:v>
+                </c:pt>
+                <c:pt idx="1012">
+                  <c:v>130.77000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1013">
+                  <c:v>131.43</c:v>
+                </c:pt>
+                <c:pt idx="1014">
+                  <c:v>131.79</c:v>
+                </c:pt>
+                <c:pt idx="1015">
+                  <c:v>131.34</c:v>
+                </c:pt>
+                <c:pt idx="1016">
+                  <c:v>131.43</c:v>
+                </c:pt>
+                <c:pt idx="1017">
+                  <c:v>131.63999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1018">
+                  <c:v>130.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1019">
+                  <c:v>129.13999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1020">
+                  <c:v>123.43</c:v>
+                </c:pt>
+                <c:pt idx="1021">
+                  <c:v>121.8</c:v>
+                </c:pt>
+                <c:pt idx="1022">
+                  <c:v>122.61</c:v>
+                </c:pt>
+                <c:pt idx="1023">
+                  <c:v>123.79</c:v>
+                </c:pt>
+                <c:pt idx="1024">
+                  <c:v>123.86</c:v>
+                </c:pt>
+                <c:pt idx="1025">
+                  <c:v>125.01</c:v>
+                </c:pt>
+                <c:pt idx="1026">
+                  <c:v>125.5</c:v>
+                </c:pt>
+                <c:pt idx="1027">
+                  <c:v>126.57</c:v>
+                </c:pt>
+                <c:pt idx="1028">
+                  <c:v>126.35</c:v>
+                </c:pt>
+                <c:pt idx="1029">
+                  <c:v>127.2</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>130.5</c:v>
+                </c:pt>
+                <c:pt idx="1031">
+                  <c:v>132.29</c:v>
+                </c:pt>
+                <c:pt idx="1032">
+                  <c:v>131.91</c:v>
+                </c:pt>
+                <c:pt idx="1033">
+                  <c:v>131.26</c:v>
+                </c:pt>
+                <c:pt idx="1034">
+                  <c:v>131.55000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1035">
+                  <c:v>128.01</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>127.31</c:v>
+                </c:pt>
+                <c:pt idx="1037">
+                  <c:v>124.36</c:v>
+                </c:pt>
+                <c:pt idx="1038">
+                  <c:v>127.31</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>126.54</c:v>
+                </c:pt>
+                <c:pt idx="1040">
+                  <c:v>130.26</c:v>
+                </c:pt>
+                <c:pt idx="1041">
+                  <c:v>130.44</c:v>
+                </c:pt>
+                <c:pt idx="1042">
+                  <c:v>130.4</c:v>
+                </c:pt>
+                <c:pt idx="1043">
+                  <c:v>128.97</c:v>
+                </c:pt>
+                <c:pt idx="1044">
+                  <c:v>132.28</c:v>
+                </c:pt>
+                <c:pt idx="1045">
+                  <c:v>133.72</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>132.43</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>132.16</c:v>
+                </c:pt>
+                <c:pt idx="1048">
+                  <c:v>130.16999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1049">
+                  <c:v>131.01</c:v>
+                </c:pt>
+                <c:pt idx="1050">
+                  <c:v>131.19</c:v>
+                </c:pt>
+                <c:pt idx="1051">
+                  <c:v>132.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1052">
+                  <c:v>132.57</c:v>
+                </c:pt>
+                <c:pt idx="1053">
+                  <c:v>135.19</c:v>
+                </c:pt>
+                <c:pt idx="1054">
+                  <c:v>135.03</c:v>
+                </c:pt>
+                <c:pt idx="1055">
+                  <c:v>135.03</c:v>
+                </c:pt>
+                <c:pt idx="1056">
+                  <c:v>135.27000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1057">
+                  <c:v>136.06</c:v>
+                </c:pt>
+                <c:pt idx="1058">
+                  <c:v>136.87</c:v>
+                </c:pt>
+                <c:pt idx="1059">
+                  <c:v>139.13</c:v>
+                </c:pt>
+                <c:pt idx="1060">
+                  <c:v>138.88</c:v>
+                </c:pt>
+                <c:pt idx="1061">
+                  <c:v>139.18</c:v>
+                </c:pt>
+                <c:pt idx="1062">
+                  <c:v>139.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1063">
+                  <c:v>138.72</c:v>
+                </c:pt>
+                <c:pt idx="1064">
+                  <c:v>137.87</c:v>
+                </c:pt>
+                <c:pt idx="1065">
+                  <c:v>138.54</c:v>
+                </c:pt>
+                <c:pt idx="1066">
+                  <c:v>137.91</c:v>
+                </c:pt>
+                <c:pt idx="1067">
+                  <c:v>142.27000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1068">
+                  <c:v>141.97999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1069">
+                  <c:v>141.46</c:v>
+                </c:pt>
+                <c:pt idx="1070">
+                  <c:v>141.54</c:v>
+                </c:pt>
+                <c:pt idx="1071">
+                  <c:v>141.82</c:v>
+                </c:pt>
+                <c:pt idx="1072">
+                  <c:v>141.61000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1073">
+                  <c:v>146.16</c:v>
+                </c:pt>
+                <c:pt idx="1074">
+                  <c:v>143.15</c:v>
+                </c:pt>
+                <c:pt idx="1075">
+                  <c:v>144.34</c:v>
+                </c:pt>
+                <c:pt idx="1076">
+                  <c:v>143.58000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1077">
+                  <c:v>145.11000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1078">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="1079">
+                  <c:v>147.13999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1080">
+                  <c:v>149.12</c:v>
+                </c:pt>
+                <c:pt idx="1081">
+                  <c:v>152.22</c:v>
+                </c:pt>
+                <c:pt idx="1082">
+                  <c:v>147.87</c:v>
+                </c:pt>
+                <c:pt idx="1083">
+                  <c:v>148.91</c:v>
+                </c:pt>
+                <c:pt idx="1084">
+                  <c:v>148.68</c:v>
+                </c:pt>
+                <c:pt idx="1085">
+                  <c:v>151.04</c:v>
+                </c:pt>
+                <c:pt idx="1086">
+                  <c:v>149.86000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1087">
+                  <c:v>152.91</c:v>
+                </c:pt>
+                <c:pt idx="1088">
+                  <c:v>153.94999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1089">
+                  <c:v>156.41999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1090">
+                  <c:v>157.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1091">
+                  <c:v>158.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1092">
+                  <c:v>160.06</c:v>
+                </c:pt>
+                <c:pt idx="1093">
+                  <c:v>161.18</c:v>
+                </c:pt>
+                <c:pt idx="1094">
+                  <c:v>163.1</c:v>
+                </c:pt>
+                <c:pt idx="1095">
+                  <c:v>166.17</c:v>
+                </c:pt>
+                <c:pt idx="1096">
+                  <c:v>165.38</c:v>
+                </c:pt>
+                <c:pt idx="1097">
+                  <c:v>163.92</c:v>
+                </c:pt>
+                <c:pt idx="1098">
+                  <c:v>162.66999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1099">
+                  <c:v>164.7</c:v>
+                </c:pt>
+                <c:pt idx="1100">
+                  <c:v>167.11</c:v>
+                </c:pt>
+                <c:pt idx="1101">
+                  <c:v>166.85</c:v>
+                </c:pt>
+                <c:pt idx="1102">
+                  <c:v>165.51</c:v>
+                </c:pt>
+                <c:pt idx="1103">
+                  <c:v>168.62</c:v>
+                </c:pt>
+                <c:pt idx="1104">
+                  <c:v>166.87</c:v>
+                </c:pt>
+                <c:pt idx="1105">
+                  <c:v>164.18</c:v>
+                </c:pt>
+                <c:pt idx="1106">
+                  <c:v>165.15</c:v>
+                </c:pt>
+                <c:pt idx="1107">
+                  <c:v>161.01</c:v>
+                </c:pt>
+                <c:pt idx="1108">
+                  <c:v>160.12</c:v>
+                </c:pt>
+                <c:pt idx="1109">
+                  <c:v>162.79</c:v>
+                </c:pt>
+                <c:pt idx="1110">
+                  <c:v>161.59</c:v>
+                </c:pt>
+                <c:pt idx="1111">
+                  <c:v>155.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1112">
+                  <c:v>154.25</c:v>
+                </c:pt>
+                <c:pt idx="1113">
+                  <c:v>153.44</c:v>
+                </c:pt>
+                <c:pt idx="1114">
+                  <c:v>154.87</c:v>
+                </c:pt>
+                <c:pt idx="1115">
+                  <c:v>154.85</c:v>
+                </c:pt>
+                <c:pt idx="1116">
+                  <c:v>149.81</c:v>
+                </c:pt>
+                <c:pt idx="1117">
+                  <c:v>148.19</c:v>
+                </c:pt>
+                <c:pt idx="1118">
+                  <c:v>146.03</c:v>
+                </c:pt>
+                <c:pt idx="1119">
+                  <c:v>148.09</c:v>
+                </c:pt>
+                <c:pt idx="1120">
+                  <c:v>148.61000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1121">
+                  <c:v>150.75</c:v>
+                </c:pt>
+                <c:pt idx="1122">
+                  <c:v>149.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1123">
+                  <c:v>148.18</c:v>
+                </c:pt>
+                <c:pt idx="1124">
+                  <c:v>150.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1125">
+                  <c:v>152.75</c:v>
+                </c:pt>
+                <c:pt idx="1126">
+                  <c:v>155.08000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1127">
+                  <c:v>154.03</c:v>
+                </c:pt>
+                <c:pt idx="1128">
+                  <c:v>152.84</c:v>
+                </c:pt>
+                <c:pt idx="1129">
+                  <c:v>151.22</c:v>
+                </c:pt>
+                <c:pt idx="1130">
+                  <c:v>154.41999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1131">
+                  <c:v>155.06</c:v>
+                </c:pt>
+                <c:pt idx="1132">
+                  <c:v>154.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1133">
+                  <c:v>154.47</c:v>
+                </c:pt>
+                <c:pt idx="1134">
+                  <c:v>153.38</c:v>
+                </c:pt>
+                <c:pt idx="1135">
+                  <c:v>152.08000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1136">
+                  <c:v>149.72999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1137">
+                  <c:v>151.97</c:v>
+                </c:pt>
+                <c:pt idx="1138">
+                  <c:v>150.99</c:v>
+                </c:pt>
+                <c:pt idx="1139">
+                  <c:v>147.97</c:v>
+                </c:pt>
+                <c:pt idx="1140">
+                  <c:v>147.32</c:v>
+                </c:pt>
+                <c:pt idx="1141">
+                  <c:v>147.47999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1142">
+                  <c:v>145.47</c:v>
+                </c:pt>
+                <c:pt idx="1143">
+                  <c:v>144.19</c:v>
+                </c:pt>
+                <c:pt idx="1144">
+                  <c:v>145.5</c:v>
+                </c:pt>
+                <c:pt idx="1145">
+                  <c:v>142.94</c:v>
+                </c:pt>
+                <c:pt idx="1146">
+                  <c:v>147.85</c:v>
+                </c:pt>
+                <c:pt idx="1147">
+                  <c:v>146.57</c:v>
+                </c:pt>
+                <c:pt idx="1148">
+                  <c:v>144.62</c:v>
+                </c:pt>
+                <c:pt idx="1149">
+                  <c:v>145.5</c:v>
+                </c:pt>
+                <c:pt idx="1150">
+                  <c:v>148.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1151">
+                  <c:v>145.38999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1152">
+                  <c:v>146.03</c:v>
+                </c:pt>
+                <c:pt idx="1153">
+                  <c:v>145.22999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1154">
+                  <c:v>148.16</c:v>
+                </c:pt>
+                <c:pt idx="1155">
+                  <c:v>149.75</c:v>
+                </c:pt>
+                <c:pt idx="1156">
+                  <c:v>149.77000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1157">
+                  <c:v>148.08000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1158">
+                  <c:v>149.15</c:v>
+                </c:pt>
+                <c:pt idx="1159">
+                  <c:v>150.44</c:v>
+                </c:pt>
+                <c:pt idx="1160">
+                  <c:v>150.44999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1161">
+                  <c:v>151.76</c:v>
+                </c:pt>
+                <c:pt idx="1162">
+                  <c:v>152.01</c:v>
+                </c:pt>
+                <c:pt idx="1163">
+                  <c:v>150.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1164">
+                  <c:v>151.12</c:v>
+                </c:pt>
+                <c:pt idx="1165">
+                  <c:v>151.4</c:v>
+                </c:pt>
+                <c:pt idx="1166">
+                  <c:v>150.16999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1167">
+                  <c:v>145.68</c:v>
+                </c:pt>
+                <c:pt idx="1168">
+                  <c:v>143.47999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1169">
+                  <c:v>143.66</c:v>
+                </c:pt>
+                <c:pt idx="1170">
+                  <c:v>148.4</c:v>
+                </c:pt>
+                <c:pt idx="1171">
+                  <c:v>149.16</c:v>
+                </c:pt>
+                <c:pt idx="1172">
+                  <c:v>146.41999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1173">
+                  <c:v>149.12</c:v>
+                </c:pt>
+                <c:pt idx="1174">
+                  <c:v>148.12</c:v>
+                </c:pt>
+                <c:pt idx="1175">
+                  <c:v>153.91999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1176">
+                  <c:v>153.07</c:v>
+                </c:pt>
+                <c:pt idx="1177">
+                  <c:v>151.56</c:v>
+                </c:pt>
+                <c:pt idx="1178">
+                  <c:v>150.93</c:v>
+                </c:pt>
+                <c:pt idx="1179">
+                  <c:v>150.88</c:v>
+                </c:pt>
+                <c:pt idx="1180">
+                  <c:v>147.08000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1181">
+                  <c:v>148.93</c:v>
+                </c:pt>
+                <c:pt idx="1182">
+                  <c:v>153.38</c:v>
+                </c:pt>
+                <c:pt idx="1183">
+                  <c:v>153.12</c:v>
+                </c:pt>
+                <c:pt idx="1184">
+                  <c:v>155.12</c:v>
+                </c:pt>
+                <c:pt idx="1185">
+                  <c:v>155.41</c:v>
+                </c:pt>
+                <c:pt idx="1186">
+                  <c:v>157.59</c:v>
+                </c:pt>
+                <c:pt idx="1187">
+                  <c:v>156.72</c:v>
+                </c:pt>
+                <c:pt idx="1188">
+                  <c:v>154.13999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1189">
+                  <c:v>159.9</c:v>
+                </c:pt>
+                <c:pt idx="1190">
+                  <c:v>155.49</c:v>
+                </c:pt>
+                <c:pt idx="1191">
+                  <c:v>157.03</c:v>
+                </c:pt>
+                <c:pt idx="1192">
+                  <c:v>155.16999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1193">
+                  <c:v>154.62</c:v>
+                </c:pt>
+                <c:pt idx="1194">
+                  <c:v>154.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1195">
+                  <c:v>153.37</c:v>
+                </c:pt>
+                <c:pt idx="1196">
+                  <c:v>150.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1197">
+                  <c:v>150.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1198">
+                  <c:v>152.72999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1199">
+                  <c:v>153.76</c:v>
+                </c:pt>
+                <c:pt idx="1200">
+                  <c:v>149.56</c:v>
+                </c:pt>
+                <c:pt idx="1201">
+                  <c:v>153.87</c:v>
+                </c:pt>
+                <c:pt idx="1202">
+                  <c:v>153.08000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1203">
+                  <c:v>156.13999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1204">
+                  <c:v>155.01</c:v>
+                </c:pt>
+                <c:pt idx="1205">
+                  <c:v>156.11000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1206">
+                  <c:v>159.85</c:v>
+                </c:pt>
+                <c:pt idx="1207">
+                  <c:v>158.83000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1208">
+                  <c:v>158.44</c:v>
+                </c:pt>
+                <c:pt idx="1209">
+                  <c:v>156.15</c:v>
+                </c:pt>
+                <c:pt idx="1210">
+                  <c:v>153.66999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1211">
+                  <c:v>153.27000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1212">
+                  <c:v>154.44</c:v>
+                </c:pt>
+                <c:pt idx="1213">
+                  <c:v>154.21</c:v>
+                </c:pt>
+                <c:pt idx="1214">
+                  <c:v>156.33000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1215">
+                  <c:v>156.79</c:v>
+                </c:pt>
+                <c:pt idx="1216">
+                  <c:v>154.61000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1217">
+                  <c:v>152.32</c:v>
+                </c:pt>
+                <c:pt idx="1218">
+                  <c:v>151.72</c:v>
+                </c:pt>
+                <c:pt idx="1219">
+                  <c:v>150.88</c:v>
+                </c:pt>
+                <c:pt idx="1220">
+                  <c:v>151.97</c:v>
+                </c:pt>
+                <c:pt idx="1221">
+                  <c:v>154.55000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1222">
+                  <c:v>160.31</c:v>
+                </c:pt>
+                <c:pt idx="1223">
+                  <c:v>156.24</c:v>
+                </c:pt>
+                <c:pt idx="1224">
+                  <c:v>158.86000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1225">
+                  <c:v>158.02000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1226">
+                  <c:v>159.97999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1227">
+                  <c:v>157.54</c:v>
+                </c:pt>
+                <c:pt idx="1228">
+                  <c:v>154.65</c:v>
+                </c:pt>
+                <c:pt idx="1229">
+                  <c:v>153.81</c:v>
+                </c:pt>
+                <c:pt idx="1230">
+                  <c:v>152.06</c:v>
+                </c:pt>
+                <c:pt idx="1231">
+                  <c:v>161.25</c:v>
+                </c:pt>
+                <c:pt idx="1232">
+                  <c:v>162.46</c:v>
+                </c:pt>
+                <c:pt idx="1233">
+                  <c:v>163.09</c:v>
+                </c:pt>
+                <c:pt idx="1234">
+                  <c:v>159.99</c:v>
+                </c:pt>
+                <c:pt idx="1235">
+                  <c:v>137.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1236">
+                  <c:v>137.47999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1237">
+                  <c:v>137.47999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1238">
+                  <c:v>137.16</c:v>
+                </c:pt>
+                <c:pt idx="1239">
+                  <c:v>138.99</c:v>
+                </c:pt>
+                <c:pt idx="1240">
+                  <c:v>138.62</c:v>
+                </c:pt>
+                <c:pt idx="1241">
+                  <c:v>138.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1242">
+                  <c:v>140.91999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1243">
+                  <c:v>140.37</c:v>
+                </c:pt>
+                <c:pt idx="1244">
+                  <c:v>140.97999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1245">
+                  <c:v>141.28</c:v>
+                </c:pt>
+                <c:pt idx="1246">
+                  <c:v>142.71</c:v>
+                </c:pt>
+                <c:pt idx="1247">
+                  <c:v>143.57</c:v>
+                </c:pt>
+                <c:pt idx="1248">
+                  <c:v>145.46</c:v>
+                </c:pt>
+                <c:pt idx="1249">
+                  <c:v>146.88</c:v>
+                </c:pt>
+                <c:pt idx="1250">
+                  <c:v>145.71</c:v>
+                </c:pt>
+                <c:pt idx="1251">
+                  <c:v>142.57</c:v>
+                </c:pt>
+                <c:pt idx="1252">
+                  <c:v>141.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1253">
+                  <c:v>141</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-8861-4E43-ACA1-95BD0591ABE8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="521122799"/>
+        <c:axId val="474776463"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="521122799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mmm\ yy" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="474776463"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="474776463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="E0E0E0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="521122799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="NVS Price Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B816B35-7C5E-C4A7-DC79-950DE6E6A8A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,25 +8331,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99103B0F-0426-407E-80D6-5D17F8719B4E}">
-  <dimension ref="A1:F1258"/>
+  <dimension ref="A1:J1258"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="5" width="11.625" customWidth="1"/>
     <col min="6" max="6" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="3.625" customWidth="1"/>
+    <col min="8" max="8" width="20.625" customWidth="1"/>
+    <col min="9" max="9" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -525,8 +8374,17 @@
       <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="9">
+        <v>44474</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>44474</v>
       </c>
@@ -545,8 +8403,15 @@
       <c r="F5" s="6">
         <v>2259554</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>44475</v>
       </c>
@@ -565,8 +8430,10 @@
       <c r="F6" s="6">
         <v>1801541</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>44476</v>
       </c>
@@ -585,8 +8452,12 @@
       <c r="F7" s="6">
         <v>2846525</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>44477</v>
       </c>
@@ -605,8 +8476,15 @@
       <c r="F8" s="6">
         <v>1613836</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="12">
+        <f ca="1">IF(ISBLANK(I5),TODAY(),I5)</f>
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>44480</v>
       </c>
@@ -625,8 +8503,15 @@
       <c r="F9" s="6">
         <v>999692</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="13">
+        <f>COUNTIF(PxDates,"&lt;"&amp;I4)+1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>44481</v>
       </c>
@@ -645,8 +8530,15 @@
       <c r="F10" s="6">
         <v>1681944</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="13">
+        <f ca="1">COUNTIF(PxDates,"&lt;="&amp;I8)</f>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>44482</v>
       </c>
@@ -665,8 +8557,15 @@
       <c r="F11" s="6">
         <v>1627489</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="13" t="str">
+        <f ca="1">IF(NOT(ISNUMBER(I4)),"Enter a start date",IF(I4&gt;I8,"Start date must be on or before end date",IF(I9&gt;I10,"No trading days between these dates","OK")))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>44483</v>
       </c>
@@ -685,8 +8584,15 @@
       <c r="F12" s="6">
         <v>1199282</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="12">
+        <f ca="1">IF($I$11="OK",INDEX(PxDates,I9),"")</f>
+        <v>44474</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>44484</v>
       </c>
@@ -705,8 +8611,15 @@
       <c r="F13" s="6">
         <v>1594227</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="12">
+        <f ca="1">IF($I$11="OK",INDEX(PxDates,I10),"")</f>
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>44487</v>
       </c>
@@ -725,8 +8638,15 @@
       <c r="F14" s="6">
         <v>1542914</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="14">
+        <f ca="1">IF($I$11="OK",INDEX(PxClose,I9),"")</f>
+        <v>79.164299999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>44488</v>
       </c>
@@ -745,8 +8665,15 @@
       <c r="F15" s="6">
         <v>1587923</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H15" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="14">
+        <f ca="1">IF($I$11="OK",INDEX(PxClose,I10),"")</f>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>44489</v>
       </c>
@@ -765,8 +8692,15 @@
       <c r="F16" s="6">
         <v>2282294</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H16" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="16">
+        <f ca="1">IF($I$11="OK",I15/I14-1,"")</f>
+        <v>0.78110587727043646</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>44490</v>
       </c>
@@ -786,7 +8720,7 @@
         <v>2165193</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>44491</v>
       </c>
@@ -805,8 +8739,12 @@
       <c r="F18" s="6">
         <v>1505336</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H18" s="1" t="str">
+        <f ca="1">IF($I$11&lt;&gt;"OK",$I$11,"NVS "&amp;IF(I16&gt;=0,"rose ","fell ")&amp;TEXT(ABS(I16),"0.0%")&amp;" from "&amp;TEXT(I14,"$#,##0.00")&amp;" on "&amp;TEXT(I12,"mmm d, yyyy")&amp;" to "&amp;TEXT(I15,"$#,##0.00")&amp;" on "&amp;TEXT(I13,"mmm d, yyyy")&amp;".")</f>
+        <v>NVS rose 78.1% from $79.16 on Oct 5, 2021 to $141.00 on Oct 2, 2026.</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>44494</v>
       </c>
@@ -826,7 +8764,7 @@
         <v>2095549</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>44495</v>
       </c>
@@ -846,7 +8784,7 @@
         <v>3513964</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>44496</v>
       </c>
@@ -866,7 +8804,7 @@
         <v>3539856</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>44497</v>
       </c>
@@ -886,7 +8824,7 @@
         <v>2639455</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>44498</v>
       </c>
@@ -906,7 +8844,7 @@
         <v>2503427</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>44501</v>
       </c>
@@ -926,7 +8864,7 @@
         <v>1970382</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>44502</v>
       </c>
@@ -946,7 +8884,7 @@
         <v>2559893</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>44503</v>
       </c>
@@ -966,7 +8904,7 @@
         <v>2519183</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>44504</v>
       </c>
@@ -986,7 +8924,7 @@
         <v>3037003</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>44505</v>
       </c>
@@ -1006,7 +8944,7 @@
         <v>2393614</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>44508</v>
       </c>
@@ -1026,7 +8964,7 @@
         <v>2232171</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>44509</v>
       </c>
@@ -1046,7 +8984,7 @@
         <v>2026679</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>44510</v>
       </c>
@@ -1066,7 +9004,7 @@
         <v>2509039</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>44511</v>
       </c>
@@ -25608,6 +33546,24 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:F1258" xr:uid="{99103B0F-0426-407E-80D6-5D17F8719B4E}"/>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>AND($I$11="OK",$I$16&gt;=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>AND($I$11="OK",$I$16&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$I$11&lt;&gt;"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid date" error="Please enter a date, e.g. 2024-01-31." sqref="I4:I5" xr:uid="{30F3AF47-48BC-47F9-B534-97D6B1293CD2}">
+      <formula1>32874</formula1>
+      <formula2>73415</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>